--- a/SGC-CKN/Excel/1d65cae2-720c-4dc7-b386-fba0bbd3ffdb_P7-48_P7-48_D800_08-03-2026.xlsx
+++ b/SGC-CKN/Excel/1d65cae2-720c-4dc7-b386-fba0bbd3ffdb_P7-48_P7-48_D800_08-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
@@ -106,6 +106,12 @@
     <t/>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+  </si>
+  <si>
     <t xml:space="preserve">08:25
 08/03/2026</t>
   </si>
@@ -114,12 +120,6 @@
 08/03/2026</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
@@ -174,7 +174,7 @@
 08/03/2026</t>
   </si>
   <si>
-    <t>16.1</t>
+    <t>8</t>
   </si>
   <si>
     <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
@@ -198,14 +198,14 @@
 08/03/2026</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc TT rất chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">15:08
 08/03/2026</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -370,17 +370,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -547,17 +547,17 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -666,7 +666,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -1026,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1226,424 +1226,356 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
       <c r="G11" s="5">
-        <v>-2.2</v>
+        <v>-3.55</v>
       </c>
       <c r="H11" s="5">
         <v>0.33</v>
       </c>
       <c r="I11" s="5">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="J11" s="8">
-        <v>6.6</v>
+        <v>3.81</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="5">
-        <v>-2.2</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="D12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="9">
         <v>-3.55</v>
       </c>
-      <c r="H12" s="5">
+      <c r="G12" s="9">
+        <v>-10.05</v>
+      </c>
+      <c r="H12" s="9">
         <v>1.17</v>
       </c>
-      <c r="I12" s="5">
-        <v>1.35</v>
-      </c>
-      <c r="J12" s="9">
-        <v>1.16</v>
-      </c>
-      <c r="K12" s="6" t="s">
+      <c r="I12" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="J12" s="12">
+        <v>5.57</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="10">
-        <v>-3.55</v>
-      </c>
-      <c r="G13" s="10">
+      <c r="A13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="13">
         <v>-10.05</v>
       </c>
-      <c r="H13" s="10">
-        <v>1.17</v>
-      </c>
-      <c r="I13" s="10">
-        <v>6.5</v>
+      <c r="G13" s="13">
+        <v>-12.05</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="I13" s="13">
+        <v>2</v>
       </c>
       <c r="J13" s="8">
-        <v>5.57</v>
-      </c>
-      <c r="K13" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="A14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="13">
-        <v>-10.05</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="E14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="16">
         <v>-12.05</v>
       </c>
-      <c r="H14" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="I14" s="13">
-        <v>2</v>
-      </c>
-      <c r="J14" s="9">
-        <v>5</v>
-      </c>
-      <c r="K14" s="14" t="s">
+      <c r="G14" s="16">
+        <v>-19.25</v>
+      </c>
+      <c r="H14" s="16">
+        <v>1</v>
+      </c>
+      <c r="I14" s="16">
+        <v>7.2</v>
+      </c>
+      <c r="J14" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="K14" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="18" t="s">
+      <c r="A15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="16">
-        <v>-12.05</v>
-      </c>
-      <c r="G15" s="16">
+      <c r="E15" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="19">
         <v>-19.25</v>
       </c>
-      <c r="H15" s="16">
-        <v>1</v>
-      </c>
-      <c r="I15" s="16">
-        <v>7.2</v>
-      </c>
-      <c r="J15" s="8">
-        <v>7.2</v>
-      </c>
-      <c r="K15" s="17" t="s">
+      <c r="G15" s="19">
+        <v>-19.55</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0.67</v>
+      </c>
+      <c r="I15" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="J15" s="22">
+        <v>0.45</v>
+      </c>
+      <c r="K15" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="21" t="s">
+      <c r="A16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="19">
-        <v>-19.25</v>
-      </c>
-      <c r="G16" s="19">
+      <c r="E16" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="23">
         <v>-19.55</v>
       </c>
-      <c r="H16" s="19">
-        <v>0.67</v>
-      </c>
-      <c r="I16" s="19">
+      <c r="G16" s="23">
+        <v>-23.55</v>
+      </c>
+      <c r="H16" s="23">
+        <v>1.92</v>
+      </c>
+      <c r="I16" s="23">
+        <v>4</v>
+      </c>
+      <c r="J16" s="8">
+        <v>2.09</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="26">
+        <v>-23.55</v>
+      </c>
+      <c r="G17" s="26">
+        <v>-33.55</v>
+      </c>
+      <c r="H17" s="26">
+        <v>0.48</v>
+      </c>
+      <c r="I17" s="26">
+        <v>10</v>
+      </c>
+      <c r="J17" s="12">
+        <v>20.69</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="29">
+        <v>-33.55</v>
+      </c>
+      <c r="G18" s="29">
+        <v>-37.55</v>
+      </c>
+      <c r="H18" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="I18" s="29">
+        <v>4</v>
+      </c>
+      <c r="J18" s="12">
+        <v>20</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="32">
+        <v>-37.55</v>
+      </c>
+      <c r="G19" s="32">
+        <v>-39.5</v>
+      </c>
+      <c r="H19" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="32">
+        <v>1.95</v>
+      </c>
+      <c r="J19" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="K19" s="33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="35">
+        <v>-39.5</v>
+      </c>
+      <c r="G20" s="35">
+        <v>-45.45</v>
+      </c>
+      <c r="H20" s="35">
         <v>0.3</v>
       </c>
-      <c r="J16" s="22">
-        <v>0.45</v>
-      </c>
-      <c r="K16" s="20" t="s">
+      <c r="I20" s="35">
+        <v>5.95</v>
+      </c>
+      <c r="J20" s="12">
+        <v>19.83</v>
+      </c>
+      <c r="K20" s="36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="23">
-        <v>-19.55</v>
-      </c>
-      <c r="G17" s="23">
-        <v>-23.55</v>
-      </c>
-      <c r="H17" s="23">
-        <v>1.92</v>
-      </c>
-      <c r="I17" s="23">
-        <v>4</v>
-      </c>
-      <c r="J17" s="9">
-        <v>2.09</v>
-      </c>
-      <c r="K17" s="24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="26">
-        <v>-23.55</v>
-      </c>
-      <c r="G18" s="26">
-        <v>-33.55</v>
-      </c>
-      <c r="H18" s="26">
-        <v>0.48</v>
-      </c>
-      <c r="I18" s="26">
-        <v>10</v>
-      </c>
-      <c r="J18" s="8">
-        <v>20.69</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="29">
-        <v>-33.55</v>
-      </c>
-      <c r="G19" s="29">
-        <v>-36.05</v>
-      </c>
-      <c r="H19" s="29">
-        <v>0.2</v>
-      </c>
-      <c r="I19" s="29">
-        <v>2.5</v>
-      </c>
-      <c r="J19" s="8">
-        <v>12.5</v>
-      </c>
-      <c r="K19" s="30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="32">
-        <v>-36.05</v>
-      </c>
-      <c r="G20" s="32">
-        <v>-37.55</v>
-      </c>
-      <c r="H20" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="I20" s="32">
-        <v>1.5</v>
-      </c>
-      <c r="J20" s="9">
-        <v>3</v>
-      </c>
-      <c r="K20" s="33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="32">
-        <v>-37.55</v>
-      </c>
-      <c r="G21" s="32">
-        <v>-41.55</v>
-      </c>
-      <c r="H21" s="32">
-        <v>0.3</v>
-      </c>
-      <c r="I21" s="32">
-        <v>4</v>
-      </c>
-      <c r="J21" s="8">
-        <v>13.33</v>
-      </c>
-      <c r="K21" s="33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="35">
-        <v>-41.55</v>
-      </c>
-      <c r="G22" s="35">
-        <v>-45.45</v>
-      </c>
-      <c r="H22" s="35">
-        <v>0.3</v>
-      </c>
-      <c r="I22" s="35">
-        <v>3.9</v>
-      </c>
-      <c r="J22" s="8">
-        <v>13</v>
-      </c>
-      <c r="K22" s="36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
+    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-    </row>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1702,8 +1634,6 @@
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1714,7 +1644,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A23:K23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1775,50 +1705,50 @@
         <v>26</v>
       </c>
       <c r="D2" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
       <c r="F2" s="5">
         <v>-3.55</v>
       </c>
       <c r="G2" s="5">
-        <v>1.5</v>
+        <v>0.33</v>
       </c>
       <c r="H2" s="5">
-        <v>3.55</v>
-      </c>
-      <c r="I2" s="9">
-        <v>2.37</v>
+        <v>1.27</v>
+      </c>
+      <c r="I2" s="8">
+        <v>3.81</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="B3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="9">
         <v>1</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>-3.55</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>-10.05</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>1.17</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>6.5</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="12">
         <v>5.57</v>
       </c>
     </row>
@@ -1847,7 +1777,7 @@
       <c r="H4" s="13">
         <v>2</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>5</v>
       </c>
     </row>
@@ -1876,7 +1806,7 @@
       <c r="H5" s="16">
         <v>7.2</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="12">
         <v>7.2</v>
       </c>
     </row>
@@ -1934,7 +1864,7 @@
       <c r="H7" s="23">
         <v>4</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>2.09</v>
       </c>
     </row>
@@ -1963,7 +1893,7 @@
       <c r="H8" s="26">
         <v>10</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="12">
         <v>20.69</v>
       </c>
     </row>
@@ -1984,16 +1914,16 @@
         <v>-33.55</v>
       </c>
       <c r="F9" s="29">
-        <v>-36.05</v>
+        <v>-37.55</v>
       </c>
       <c r="G9" s="29">
         <v>0.2</v>
       </c>
       <c r="H9" s="29">
-        <v>2.5</v>
-      </c>
-      <c r="I9" s="8">
-        <v>12.5</v>
+        <v>4</v>
+      </c>
+      <c r="I9" s="12">
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2007,22 +1937,22 @@
         <v>55</v>
       </c>
       <c r="D10" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="32">
-        <v>-36.05</v>
+        <v>-37.55</v>
       </c>
       <c r="F10" s="32">
-        <v>-41.55</v>
+        <v>-39.5</v>
       </c>
       <c r="G10" s="32">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="32">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="I10" s="8">
-        <v>6.88</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2033,13 +1963,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <v>-41.55</v>
+        <v>-39.5</v>
       </c>
       <c r="F11" s="35">
         <v>-45.45</v>
@@ -2048,10 +1978,10 @@
         <v>0.3</v>
       </c>
       <c r="H11" s="35">
-        <v>3.9</v>
-      </c>
-      <c r="I11" s="8">
-        <v>13</v>
+        <v>5.95</v>
+      </c>
+      <c r="I11" s="12">
+        <v>19.83</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2065,22 +1995,22 @@
         <v>29</v>
       </c>
       <c r="D12" s="40">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
       <c r="F12" s="40">
         <v>-45.45</v>
       </c>
       <c r="G12" s="40">
-        <v>8.43</v>
+        <v>6.97</v>
       </c>
       <c r="H12" s="40">
-        <v>45.45</v>
+        <v>43.17</v>
       </c>
       <c r="I12" s="40">
-        <v>5.39</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/1d65cae2-720c-4dc7-b386-fba0bbd3ffdb_P7-48_P7-48_D800_08-03-2026.xlsx
+++ b/SGC-CKN/Excel/1d65cae2-720c-4dc7-b386-fba0bbd3ffdb_P7-48_P7-48_D800_08-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
@@ -106,12 +106,6 @@
     <t/>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
     <t xml:space="preserve">08:25
 08/03/2026</t>
   </si>
@@ -120,6 +114,12 @@
 08/03/2026</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
@@ -174,7 +174,7 @@
 08/03/2026</t>
   </si>
   <si>
-    <t>8</t>
+    <t>16.1</t>
   </si>
   <si>
     <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
@@ -198,14 +198,14 @@
 08/03/2026</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">15:08
 08/03/2026</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -370,17 +370,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -547,17 +547,17 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -666,7 +666,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -1026,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1226,356 +1226,424 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>-2.28</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-3.55</v>
+        <v>-2.2</v>
       </c>
       <c r="H11" s="5">
         <v>0.33</v>
       </c>
       <c r="I11" s="5">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="J11" s="8">
-        <v>3.81</v>
+        <v>6.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="F12" s="5">
+        <v>-2.2</v>
+      </c>
+      <c r="G12" s="5">
+        <v>-3.55</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1.17</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1.35</v>
+      </c>
+      <c r="J12" s="9">
+        <v>1.16</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="B13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="9">
+      <c r="D13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="10">
         <v>-3.55</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G13" s="10">
         <v>-10.05</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H13" s="10">
         <v>1.17</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I13" s="10">
         <v>6.5</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J13" s="8">
         <v>5.57</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K13" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="B14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F14" s="13">
         <v>-10.05</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G14" s="13">
         <v>-12.05</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H14" s="13">
         <v>0.4</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I14" s="13">
         <v>2</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J14" s="9">
         <v>5</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K14" s="14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="B15" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D15" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F15" s="16">
         <v>-12.05</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G15" s="16">
         <v>-19.25</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H15" s="16">
         <v>1</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I15" s="16">
         <v>7.2</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J15" s="8">
         <v>7.2</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K15" s="17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B16" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D16" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F16" s="19">
         <v>-19.25</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G16" s="19">
         <v>-19.55</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H16" s="19">
         <v>0.67</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I16" s="19">
         <v>0.3</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J16" s="22">
         <v>0.45</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K16" s="20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="B17" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D17" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F17" s="23">
         <v>-19.55</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G17" s="23">
         <v>-23.55</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H17" s="23">
         <v>1.92</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I17" s="23">
         <v>4</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J17" s="9">
         <v>2.09</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K17" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="B18" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D18" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E18" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F18" s="26">
         <v>-23.55</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G18" s="26">
         <v>-33.55</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H18" s="26">
         <v>0.48</v>
       </c>
-      <c r="I17" s="26">
-        <v>10</v>
-      </c>
-      <c r="J17" s="12">
+      <c r="I18" s="26">
+        <v>10</v>
+      </c>
+      <c r="J18" s="8">
         <v>20.69</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K18" s="27" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="30" t="s">
+      <c r="B19" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D19" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E19" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F19" s="29">
         <v>-33.55</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G19" s="29">
+        <v>-36.05</v>
+      </c>
+      <c r="H19" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="I19" s="29">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="8">
+        <v>12.5</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="32">
+        <v>-36.05</v>
+      </c>
+      <c r="G20" s="32">
         <v>-37.55</v>
       </c>
-      <c r="H18" s="29">
-        <v>0.2</v>
-      </c>
-      <c r="I18" s="29">
+      <c r="H20" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="J20" s="9">
+        <v>3</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="32">
+        <v>-37.55</v>
+      </c>
+      <c r="G21" s="32">
+        <v>-41.55</v>
+      </c>
+      <c r="H21" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="I21" s="32">
         <v>4</v>
       </c>
-      <c r="J18" s="12">
-        <v>20</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="34" t="s">
+      <c r="J21" s="8">
+        <v>13.33</v>
+      </c>
+      <c r="K21" s="33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="32">
-        <v>-37.55</v>
-      </c>
-      <c r="G19" s="32">
-        <v>-39.5</v>
-      </c>
-      <c r="H19" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="32">
-        <v>1.95</v>
-      </c>
-      <c r="J19" s="8">
+      <c r="E22" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="35">
+        <v>-41.55</v>
+      </c>
+      <c r="G22" s="35">
+        <v>-45.45</v>
+      </c>
+      <c r="H22" s="35">
+        <v>0.3</v>
+      </c>
+      <c r="I22" s="35">
         <v>3.9</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="J22" s="8">
+        <v>13</v>
+      </c>
+      <c r="K22" s="36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="35">
-        <v>-39.5</v>
-      </c>
-      <c r="G20" s="35">
-        <v>-45.45</v>
-      </c>
-      <c r="H20" s="35">
-        <v>0.3</v>
-      </c>
-      <c r="I20" s="35">
-        <v>5.95</v>
-      </c>
-      <c r="J20" s="12">
-        <v>19.83</v>
-      </c>
-      <c r="K20" s="36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+    <row r="25" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-    </row>
-    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+    </row>
     <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1634,6 +1702,8 @@
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1644,7 +1714,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A25:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1705,50 +1775,50 @@
         <v>26</v>
       </c>
       <c r="D2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="5">
-        <v>-2.28</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-3.55</v>
       </c>
       <c r="G2" s="5">
-        <v>0.33</v>
+        <v>1.5</v>
       </c>
       <c r="H2" s="5">
-        <v>1.27</v>
-      </c>
-      <c r="I2" s="8">
-        <v>3.81</v>
+        <v>3.55</v>
+      </c>
+      <c r="I2" s="9">
+        <v>2.37</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="10">
         <v>1</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="10">
         <v>-3.55</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="10">
         <v>-10.05</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="10">
         <v>1.17</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <v>6.5</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>5.57</v>
       </c>
     </row>
@@ -1777,7 +1847,7 @@
       <c r="H4" s="13">
         <v>2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="9">
         <v>5</v>
       </c>
     </row>
@@ -1806,7 +1876,7 @@
       <c r="H5" s="16">
         <v>7.2</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>7.2</v>
       </c>
     </row>
@@ -1864,7 +1934,7 @@
       <c r="H7" s="23">
         <v>4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="9">
         <v>2.09</v>
       </c>
     </row>
@@ -1893,7 +1963,7 @@
       <c r="H8" s="26">
         <v>10</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>20.69</v>
       </c>
     </row>
@@ -1914,16 +1984,16 @@
         <v>-33.55</v>
       </c>
       <c r="F9" s="29">
-        <v>-37.55</v>
+        <v>-36.05</v>
       </c>
       <c r="G9" s="29">
         <v>0.2</v>
       </c>
       <c r="H9" s="29">
-        <v>4</v>
-      </c>
-      <c r="I9" s="12">
-        <v>20</v>
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="8">
+        <v>12.5</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1937,22 +2007,22 @@
         <v>55</v>
       </c>
       <c r="D10" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="32">
-        <v>-37.55</v>
+        <v>-36.05</v>
       </c>
       <c r="F10" s="32">
-        <v>-39.5</v>
+        <v>-41.55</v>
       </c>
       <c r="G10" s="32">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="32">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
       <c r="I10" s="8">
-        <v>3.9</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1963,13 +2033,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <v>-39.5</v>
+        <v>-41.55</v>
       </c>
       <c r="F11" s="35">
         <v>-45.45</v>
@@ -1978,10 +2048,10 @@
         <v>0.3</v>
       </c>
       <c r="H11" s="35">
-        <v>5.95</v>
-      </c>
-      <c r="I11" s="12">
-        <v>19.83</v>
+        <v>3.9</v>
+      </c>
+      <c r="I11" s="8">
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1995,22 +2065,22 @@
         <v>29</v>
       </c>
       <c r="D12" s="40">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E12" s="40">
-        <v>-2.28</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-45.45</v>
       </c>
       <c r="G12" s="40">
-        <v>6.97</v>
+        <v>8.43</v>
       </c>
       <c r="H12" s="40">
-        <v>43.17</v>
+        <v>45.45</v>
       </c>
       <c r="I12" s="40">
-        <v>6.2</v>
+        <v>5.39</v>
       </c>
     </row>
   </sheetData>
